--- a/data/monitored_laws.xlsx
+++ b/data/monitored_laws.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -803,7 +803,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>보헙업법</t>
+          <t>본인서명사실 확인 등에 관한 법률</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -811,7 +811,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>본인서명사실 확인 등에 관한 법률</t>
+          <t>금융회사지배구조 감독규정</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -819,7 +819,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>금융회사지배구조 감독규정</t>
+          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -827,7 +827,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
+          <t>개인정보 처리방법에 관한 고시</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -835,7 +835,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>개인정보 처리방법에 관한 고시</t>
+          <t>퇴직연금감독규정</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -843,7 +843,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>퇴직연금감독규정</t>
+          <t>금융투자업규정</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -851,7 +851,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>남녀공용평등과 일가정양립지원에 관한 법률</t>
+          <t>외부감사 및 회계 등에 관한 규정</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -859,7 +859,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>금융투자업규정</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -867,7 +867,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>외부감사 및 회계 등에 관한 규정</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -875,7 +875,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
+          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -883,7 +883,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -891,7 +891,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>교육세법</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -899,7 +899,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
+          <t>장애인차별금지 및 권리구제 등에 관한 법률</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -907,7 +907,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>교육세법</t>
+          <t>근로자참여 및 협력증진에 관한 법률</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -915,7 +915,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>장애인차별금지 및 권리구제 등에 관한 법률</t>
+          <t>방문판매등에 관한 법률</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -923,7 +923,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>근로자참여 및 협력증진에 관한 법률</t>
+          <t>부당한지원행위의 심사지침</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -931,7 +931,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>방문판매등에 관한 법률</t>
+          <t>국민건강보험법</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -939,7 +939,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>신용정보 이용 및 보호에 관한 법률</t>
+          <t>전자문서 및 전자거래 기본법</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -947,7 +947,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>부당한지원행위의 심사지침</t>
+          <t>전자서명법</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -955,7 +955,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>국민건강보험법</t>
+          <t>소방기본법</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -963,7 +963,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>전자문서 및 전자거래 기본법</t>
+          <t>근로자퇴직급여보장법</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -971,7 +971,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>전자서명법</t>
+          <t>고용상 연령금지 및 고령자고용촉진에 관한 법률</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -979,7 +979,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>소방기본법</t>
+          <t>근로자퇴직급여보장법 및 퇴직연금감독규정</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -987,7 +987,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>근로자퇴직급여보장법</t>
+          <t>여성의 경제활동 촉진과 경력단절 예방법</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -995,7 +995,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>고용상 연령금지 및 고령자고용촉진에 관한 법률</t>
+          <t>노후준비지원법</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>근로자퇴직급여보장법 및 퇴직연금감독규정</t>
+          <t>영유아보육법</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1011,7 +1011,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>여성의 경제활동 촉진과 경력단절 예방법</t>
+          <t>공직자의 이해충돌방지법</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1019,7 +1019,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>노후준비지원법</t>
+          <t>남녀고용평등법</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1027,7 +1027,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>영유아보육법</t>
+          <t>퇴직연금감독규정 일부개정안</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1035,7 +1035,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>공직자의 이해충돌방지법</t>
+          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1043,7 +1043,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>남녀고용평등법</t>
+          <t>금융회사 등의 해외진출에 관한 규정</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1051,7 +1051,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>퇴직연금감독규정 일부개정안</t>
+          <t>금융기관검사 및 제재에 관한 규정</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1059,7 +1059,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
+          <t>중대재해 처벌 등에 관한 법률</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
@@ -1067,42 +1067,10 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>금융회사 등의 해외진출에 관한 규정</t>
+          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>금융기관검사 및 제재에 관한 규정</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>중대재해 처벌 등에 관한 법률</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>특정 금융거래정보의 보고 및 이용에 관한 법률</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/monitored_laws.xlsx
+++ b/data/monitored_laws.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>법령명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -1103,6 +1091,30 @@
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>조세특례제한법</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>조세특례제한법 시행령</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>조세특례제한법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/monitored_laws.xlsx
+++ b/data/monitored_laws.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,16 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:B76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>법령명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -523,7 +511,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>증권의 발생 및 공시 등에 관한 규정</t>
+          <t>증권의 발행 및 공시에 관한 규정</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -555,7 +543,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>증권의 발행 및 공시에 관한 규정</t>
+          <t>예금자보호법</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -563,7 +551,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>예금자보호법</t>
+          <t>소득세법</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -571,7 +559,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>소득세법</t>
+          <t>국민연금법</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -579,7 +567,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>국민연금법</t>
+          <t>근로복지기본법</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -587,7 +575,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>근로복지기본법</t>
+          <t>주식회사 등의 외부감사에 관한 법률</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -595,7 +583,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>주식회사 등의 외부감사에 관한 법률</t>
+          <t>개인정보 보호법</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -603,7 +591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>민사소송법</t>
+          <t>개인정보보호법</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -611,7 +599,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>개인정보보호법</t>
+          <t>남녀고용평등과 일ㆍ가정 양립 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -619,7 +607,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>근로기준법</t>
+          <t>남녀고용평등과 일·가정 양립 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -627,7 +615,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>남녀고용평등과 일·가정 양립 지원에 관한 법률</t>
+          <t>전자금융감독규정</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -635,7 +623,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>전자금융감독규정</t>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -643,7 +631,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률</t>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지 관리규정</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -651,7 +639,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>공중 등 협박목적을 위한 자금조달행위의 금지 관리규정</t>
+          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -659,7 +647,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률</t>
+          <t>법인세법</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -667,7 +655,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>법인세법</t>
+          <t>법인의 등기에 관한 특례법</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -675,7 +663,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>법인의 등기에 관한 특례법</t>
+          <t>상업등기법</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -683,7 +671,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>상업등기법</t>
+          <t>민법</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -691,7 +679,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>민법</t>
+          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -699,7 +687,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률</t>
+          <t>양육비 이행확보 및 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -707,7 +695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>양육비 이행확보 및 지원에 관한 법률</t>
+          <t>보험사기업무감독규정</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -715,7 +703,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>보험사기업무감독규정</t>
+          <t>신용정보업감독규정</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -723,7 +711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>신용정보업감독규정</t>
+          <t>부정청탁 및 금품등 수수의 금지에 관한 법률</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -731,7 +719,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>부정청탁 및 금품등 수수의 금지에 관한 법률</t>
+          <t>전기통신금융사기 피해 방지 및 피해금 환급에 관한 특별법</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -739,7 +727,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>보험사기방지 특별법</t>
+          <t>전기통신금융사기 피해방지 및 피해금 환급에 관한 특별법</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -747,7 +735,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>전기통신금융사기 피해방지 및 피해금 환급에 관한 특별법</t>
+          <t>금융회사의 지배구조에 관한 법률</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -755,7 +743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>금융회사의 지배구조에 관한 법률</t>
+          <t>특정 금융거래정보의 보고 및 이용 등에 관한 법률</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -763,7 +751,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>가상자산 이용자 보호 등에 관한 법률</t>
+          <t>특정금융거래정보의 보고 및 이용 등에 관한 법률</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -771,7 +759,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>특정금융거래정보의 보고 및 이용 등에 관한 법률</t>
+          <t>독점규제 및 공정거래에 관한 법률</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -779,7 +767,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>자본시장법</t>
+          <t>금융복합기업집단 감독규정</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -787,7 +775,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>독점규제 및 공정거래에 관한 법률</t>
+          <t>본인서명사실 확인 등에 관한 법률</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -795,7 +783,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>금융복합기업집단 감독규정</t>
+          <t>금융회사지배구조 감독규정</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -803,7 +791,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>본인서명사실 확인 등에 관한 법률</t>
+          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -811,7 +799,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>금융회사지배구조 감독규정</t>
+          <t>개인정보 처리방법에 관한 고시</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -819,7 +807,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
+          <t>퇴직연금감독규정</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -827,7 +815,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>개인정보 처리방법에 관한 고시</t>
+          <t>금융투자업규정</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -835,7 +823,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>퇴직연금감독규정</t>
+          <t>외부감사 및 회계 등에 관한 규정</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -843,7 +831,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>금융투자업규정</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -851,7 +839,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>외부감사 및 회계 등에 관한 규정</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -859,7 +847,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
+          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -867,7 +855,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -875,7 +863,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>교육세법</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -883,7 +871,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
+          <t>방문판매 등에 관한 법률</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -891,7 +879,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>교육세법</t>
+          <t>근로자참여 및 협력증진에 관한 법률</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -899,7 +887,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>장애인차별금지 및 권리구제 등에 관한 법률</t>
+          <t>방문판매등에 관한 법률</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -907,7 +895,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>근로자참여 및 협력증진에 관한 법률</t>
+          <t>부당한지원행위의 심사지침</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -915,7 +903,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>방문판매등에 관한 법률</t>
+          <t>국민건강보험법</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -923,7 +911,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>부당한지원행위의 심사지침</t>
+          <t>전자문서 및 전자거래 기본법</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -931,7 +919,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>국민건강보험법</t>
+          <t>전자서명법</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -939,7 +927,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>전자문서 및 전자거래 기본법</t>
+          <t>소방기본법</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -947,7 +935,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>전자서명법</t>
+          <t>근로자퇴직급여보장법</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -955,7 +943,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>소방기본법</t>
+          <t>노후준비 지원법</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -963,7 +951,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>근로자퇴직급여보장법</t>
+          <t>공직자의 이해충돌 방지법</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -971,7 +959,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>고용상 연령금지 및 고령자고용촉진에 관한 법률</t>
+          <t>노후준비지원법</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -979,7 +967,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>근로자퇴직급여보장법 및 퇴직연금감독규정</t>
+          <t>영유아보육법</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -987,7 +975,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>여성의 경제활동 촉진과 경력단절 예방법</t>
+          <t>공직자의 이해충돌방지법</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -995,7 +983,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>노후준비지원법</t>
+          <t>남녀고용평등법</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -1003,7 +991,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>영유아보육법</t>
+          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -1011,7 +999,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>공직자의 이해충돌방지법</t>
+          <t>금융회사 등의 해외진출에 관한 규정</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1019,7 +1007,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>남녀고용평등법</t>
+          <t>금융기관검사 및 제재에 관한 규정</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1027,7 +1015,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>퇴직연금감독규정 일부개정안</t>
+          <t>중대재해 처벌 등에 관한 법률</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1035,42 +1023,10 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
+          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>금융회사 등의 해외진출에 관한 규정</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr"/>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>금융기관검사 및 제재에 관한 규정</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>중대재해 처벌 등에 관한 법률</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/monitored_laws.xlsx
+++ b/data/monitored_laws.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1028,6 +1028,30 @@
       </c>
       <c r="B76" t="inlineStr"/>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>근로기준법</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>근로기준법 시행령</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>근로기준법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/monitored_laws.xlsx
+++ b/data/monitored_laws.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B79"/>
+  <dimension ref="A1:B169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -591,7 +591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>개인정보보호법</t>
+          <t>남녀고용평등과 일ㆍ가정 양립 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -599,7 +599,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>남녀고용평등과 일ㆍ가정 양립 지원에 관한 법률</t>
+          <t>전자금융감독규정</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>남녀고용평등과 일·가정 양립 지원에 관한 법률</t>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -615,7 +615,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>전자금융감독규정</t>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지 관리규정</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -623,7 +623,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률</t>
+          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -631,7 +631,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>공중 등 협박목적을 위한 자금조달행위의 금지 관리규정</t>
+          <t>법인세법</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -639,7 +639,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률</t>
+          <t>법인의 등기에 관한 특례법</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -647,7 +647,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>법인세법</t>
+          <t>상업등기법</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -655,7 +655,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>법인의 등기에 관한 특례법</t>
+          <t>민법</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -663,7 +663,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>상업등기법</t>
+          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>민법</t>
+          <t>양육비 이행확보 및 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -679,7 +679,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률</t>
+          <t>보험사기업무감독규정</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -687,7 +687,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>양육비 이행확보 및 지원에 관한 법률</t>
+          <t>신용정보업감독규정</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
@@ -695,7 +695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>보험사기업무감독규정</t>
+          <t>부정청탁 및 금품등 수수의 금지에 관한 법률</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>신용정보업감독규정</t>
+          <t>전기통신금융사기 피해 방지 및 피해금 환급에 관한 특별법</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -711,7 +711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>부정청탁 및 금품등 수수의 금지에 관한 법률</t>
+          <t>금융회사의 지배구조에 관한 법률</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -719,7 +719,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>전기통신금융사기 피해 방지 및 피해금 환급에 관한 특별법</t>
+          <t>특정 금융거래정보의 보고 및 이용 등에 관한 법률</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -727,7 +727,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>전기통신금융사기 피해방지 및 피해금 환급에 관한 특별법</t>
+          <t>독점규제 및 공정거래에 관한 법률</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -735,7 +735,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>금융회사의 지배구조에 관한 법률</t>
+          <t>금융복합기업집단 감독규정</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -743,7 +743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>특정 금융거래정보의 보고 및 이용 등에 관한 법률</t>
+          <t>본인서명사실 확인 등에 관한 법률</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -751,7 +751,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>특정금융거래정보의 보고 및 이용 등에 관한 법률</t>
+          <t>금융회사지배구조 감독규정</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>독점규제 및 공정거래에 관한 법률</t>
+          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -767,7 +767,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>금융복합기업집단 감독규정</t>
+          <t>개인정보 처리방법에 관한 고시</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -775,7 +775,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>본인서명사실 확인 등에 관한 법률</t>
+          <t>퇴직연금감독규정</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -783,7 +783,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>금융회사지배구조 감독규정</t>
+          <t>금융투자업규정</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>특정 금융거래정보 보고 등에 관한 검사 및 제재규정</t>
+          <t>외부감사 및 회계 등에 관한 규정</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
@@ -799,7 +799,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>개인정보 처리방법에 관한 고시</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
@@ -807,7 +807,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>퇴직연금감독규정</t>
+          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
@@ -815,7 +815,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>금융투자업규정</t>
+          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -823,7 +823,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>외부감사 및 회계 등에 관한 규정</t>
+          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -831,7 +831,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시에 관한 규정</t>
+          <t>교육세법</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -839,7 +839,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>공시대상기업집단 소속회사 등의 중요사항 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>방문판매 등에 관한 법률</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
@@ -847,7 +847,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>대규모내부거래 등에 대한 이사회 의결 및 공시의무 위반사건에 관한 과태료 부과 기준</t>
+          <t>근로자참여 및 협력증진에 관한 법률</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
@@ -855,7 +855,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>특수관계인에 대한 부당한 이익제공행위 심사지침</t>
+          <t>부당한지원행위의 심사지침</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
@@ -863,7 +863,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>교육세법</t>
+          <t>국민건강보험법</t>
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
@@ -871,7 +871,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>방문판매 등에 관한 법률</t>
+          <t>전자문서 및 전자거래 기본법</t>
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
@@ -879,7 +879,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>근로자참여 및 협력증진에 관한 법률</t>
+          <t>전자서명법</t>
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
@@ -887,7 +887,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>방문판매등에 관한 법률</t>
+          <t>소방기본법</t>
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
@@ -895,7 +895,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>부당한지원행위의 심사지침</t>
+          <t>근로자퇴직급여보장법</t>
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
@@ -903,7 +903,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>국민건강보험법</t>
+          <t>노후준비 지원법</t>
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
@@ -911,7 +911,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>전자문서 및 전자거래 기본법</t>
+          <t>공직자의 이해충돌 방지법</t>
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
@@ -919,7 +919,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>전자서명법</t>
+          <t>영유아보육법</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
@@ -927,7 +927,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>소방기본법</t>
+          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
@@ -935,7 +935,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>근로자퇴직급여보장법</t>
+          <t>금융회사 등의 해외진출에 관한 규정</t>
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
@@ -943,7 +943,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>노후준비 지원법</t>
+          <t>금융기관검사 및 제재에 관한 규정</t>
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
@@ -951,7 +951,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>공직자의 이해충돌 방지법</t>
+          <t>중대재해 처벌 등에 관한 법률</t>
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
@@ -959,7 +959,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>노후준비지원법</t>
+          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
@@ -967,7 +967,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>영유아보육법</t>
+          <t>근로기준법</t>
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
@@ -975,7 +975,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>공직자의 이해충돌방지법</t>
+          <t>근로기준법 시행령</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
@@ -983,7 +983,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>남녀고용평등법</t>
+          <t>근로기준법 시행규칙</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
@@ -991,7 +991,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>데이터 산업진흥 및 이용촉진에 관한 기본법</t>
+          <t>서민의 금융생활 지원에 관한 법률</t>
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
@@ -999,7 +999,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>금융회사 등의 해외진출에 관한 규정</t>
+          <t>서민의 금융생활 지원에 관한 법률 시행령</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -1007,7 +1007,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>금융기관검사 및 제재에 관한 규정</t>
+          <t>서민의 금융생활 지원에 관한 법률 시행규칙</t>
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>중대재해 처벌 등에 관한 법률</t>
+          <t>국세기본법</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
@@ -1023,7 +1023,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>가명정보의 결합 및 반출 등에 관한 고시</t>
+          <t>국세기본법 시행령</t>
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>근로기준법</t>
+          <t>국세기본법 시행규칙</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>근로기준법 시행령</t>
+          <t>지방세법</t>
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
@@ -1047,10 +1047,730 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>근로기준법 시행규칙</t>
+          <t>지방세법 시행령</t>
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>지방세법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>조세특례제한법</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>조세특례제한법 시행령</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>조세특례제한법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>소득세법 시행령</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>소득세법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>국민건강보험법 시행령</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>국민건강보험법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>인공지능 발전과 신뢰 기반 조성 등에 관한 기본법 시행령</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>인공지능 발전과 신뢰 기반 조성 등에 관한 기본법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>민사집행법 시행령</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>민사집행법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>보험업법 시행령</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>보험업법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>자본시장과 금융투자업에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>자본시장과 금융투자업에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>금융소비자 보호에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>금융소비자 보호에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>고용보험법 시행령</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>고용보험법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>신용정보의 이용 및 보호에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>신용정보의 이용 및 보호에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>노동조합 및 노동관계조정법 시행령</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>노동조합 및 노동관계조정법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>상법 시행령</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>상법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>예금자보호법 시행령</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>예금자보호법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>국민연금법 시행령</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>국민연금법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>근로복지기본법 시행령</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>근로복지기본법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>주식회사 등의 외부감사에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>주식회사 등의 외부감사에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>개인정보 보호법 시행령</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>개인정보 보호법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>남녀고용평등과 일ㆍ가정 양립 지원에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>남녀고용평등과 일ㆍ가정 양립 지원에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>공중 등 협박목적을 위한 자금조달행위의 금지에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>민사소송 등에서의 전자문서 이용 등에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>법인세법 시행령</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>법인세법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>법인의 등기에 관한 특례법 시행령</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>법인의 등기에 관한 특례법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>상업등기법 시행령</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>상업등기법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>민법 시행령</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>민법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>개인금융채권의 관리 및 개인금융채무자의 보호에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>양육비 이행확보 및 지원에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>양육비 이행확보 및 지원에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>부정청탁 및 금품등 수수의 금지에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>부정청탁 및 금품등 수수의 금지에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>전기통신금융사기 피해 방지 및 피해금 환급에 관한 특별법 시행령</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>전기통신금융사기 피해 방지 및 피해금 환급에 관한 특별법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>금융회사의 지배구조에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>금융회사의 지배구조에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>특정 금융거래정보의 보고 및 이용 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>특정 금융거래정보의 보고 및 이용 등에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>독점규제 및 공정거래에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>독점규제 및 공정거래에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>본인서명사실 확인 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>본인서명사실 확인 등에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>교육세법 시행령</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>교육세법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>방문판매 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>방문판매 등에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>근로자참여 및 협력증진에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>근로자참여 및 협력증진에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>전자문서 및 전자거래 기본법 시행령</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>전자문서 및 전자거래 기본법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>전자서명법 시행령</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>전자서명법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>소방기본법 시행령</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>소방기본법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>근로자퇴직급여보장법 시행령</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>근로자퇴직급여보장법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>노후준비 지원법 시행령</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>노후준비 지원법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>공직자의 이해충돌 방지법 시행령</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>공직자의 이해충돌 방지법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>영유아보육법 시행령</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>영유아보육법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>데이터 산업진흥 및 이용촉진에 관한 기본법 시행령</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>데이터 산업진흥 및 이용촉진에 관한 기본법 시행규칙</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>중대재해 처벌 등에 관한 법률 시행령</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>중대재해 처벌 등에 관한 법률 시행규칙</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
